--- a/artfynd/A 3152-2023 artfynd.xlsx
+++ b/artfynd/A 3152-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3152-2023 artfynd.xlsx
+++ b/artfynd/A 3152-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>75749907</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437873.9592292903</v>
+        <v>437874</v>
       </c>
       <c r="R2" t="n">
-        <v>7014607.690445282</v>
+        <v>7014608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2015-06-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,12 +804,7 @@
         <v>92519278</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -859,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437840.1084780107</v>
+        <v>437840</v>
       </c>
       <c r="R3" t="n">
-        <v>7014583.564021618</v>
+        <v>7014584</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,19 +872,9 @@
           <t>2021-04-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-04-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,12 +905,7 @@
         <v>92520059</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437840.1084780107</v>
+        <v>437840</v>
       </c>
       <c r="R4" t="n">
-        <v>7014583.564021618</v>
+        <v>7014584</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,19 +978,9 @@
           <t>2021-04-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-04-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1054,6 +1009,966 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>101591777</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dödfallet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>437879</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7014637</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>101591672</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dödfallet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>437879</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7014637</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>56322328</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92208</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>658</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kvarnsved 8 km SO om Mörsil, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>437940</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7014637</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-06-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-06-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca. 50 ex. på murken granlåga, omkr. ca. 100 cm.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av lövträd.</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Murken granlåga. # Gran</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>69547564</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91905</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kvarnsved 8 km SO om Mörsil, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>437919</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7014619</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-06-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-06-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca. 50 ex. på bark stammen av död, stående gran, omkr. 101 cm.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av lövträd.</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark på stammen av död, stående gran. # Gran</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>75749904</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kvarnsved 8 km SO om Mörsil, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>438045</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7014679</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2015-06-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2015-06-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 dm2 på levande sälg, omkr. 111 cm.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Talldominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Levande sälg. # Sälg</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>75749905</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kvarnsved 8 km SO om Mörsil, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>438075</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7014676</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2015-06-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2015-06-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca. 50 dm2 på levande/döende asp, omkr. 64 cm.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Talldominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Levande/döende asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>75749906</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kvarnsved 8 km SO om Mörsil, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>438072</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7014669</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2015-06-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2015-06-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca. 5 dm2 (döende bålar) på död, hängande asp, omkr. 68 cm.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Talldominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Död, hängande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>75753033</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kvarnsved 8 km SO om Mörsil, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>438052</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7014682</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2015-06-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2015-06-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca. 8 dm2 på avbruten stamdel samt på den levande stammen av två ihopväxta sälgar.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Talldominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stammen av levande sälg samt avbruten stamdel av sälg. # Sälg</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3152-2023 artfynd.xlsx
+++ b/artfynd/A 3152-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56322328</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69547564</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75749904</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75749905</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,6 +1327,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75749906</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75749907</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1529,6 +1564,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92519278</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1655,6 +1695,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75753033</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1765,6 +1810,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92520059</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1867,6 +1917,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101591777</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1969,8 +2024,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101591672</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>